--- a/outbound/4_FFF_Allocation_PTLBM_202606.xlsx
+++ b/outbound/4_FFF_Allocation_PTLBM_202606.xlsx
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011503</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="K3" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M3" s="3" t="n"/>
     </row>
@@ -638,11 +638,11 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011503</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="K4" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M4" s="3" t="n"/>
     </row>
@@ -686,20 +686,20 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034274</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011020</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="K5" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M5" s="3" t="n"/>
     </row>
@@ -743,20 +743,20 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034274</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011020</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M6" s="3" t="n"/>
     </row>
@@ -800,20 +800,20 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034273</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1125122363</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M7" s="3" t="n"/>
     </row>
@@ -857,20 +857,20 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011131</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M8" s="3" t="n"/>
     </row>
@@ -914,20 +914,20 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011131</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M9" s="3" t="n"/>
     </row>
@@ -971,20 +971,20 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034273</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126010637</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M10" s="3" t="n"/>
     </row>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011446</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M11" s="3" t="n"/>
     </row>
@@ -1094,11 +1094,11 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011446</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M12" s="3" t="n"/>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126011538</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M13" s="3" t="n"/>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1208,11 +1208,11 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126011538</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M14" s="3" t="n"/>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126011213</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M15" s="3" t="n"/>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126011213</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M16" s="3" t="n"/>
     </row>
@@ -1379,11 +1379,11 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126010702</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M17" s="3" t="n"/>
     </row>
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126010702</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M18" s="3" t="n"/>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034274</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126010933</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M19" s="3" t="n"/>
     </row>
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126010643</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M20" s="3" t="n"/>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034274</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126010932</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M21" s="3" t="n"/>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1664,11 +1664,11 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126011132</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
       <c r="M22" s="3" t="n"/>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>1126011534</t>
+          <t>1126011503</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034274</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>1126010634</t>
+          <t>1126011020</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
